--- a/healthcare_assessment_forms/012_stool_consistency_assessment_questionnaire--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/012_stool_consistency_assessment_questionnaire--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1126,8 +1126,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'loose'}</t>
+          <t>loose</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Loose'}</t>
+          <t>Loose</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pellet'}</t>
+          <t>pellet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pellet'}</t>
+          <t>Pellet</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'mucous'}</t>
+          <t>mucous</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Mucous'}</t>
+          <t>Mucous</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'undigested'}</t>
+          <t>undigested</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Undigested'}</t>
+          <t>Undigested</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'diarrhea'}</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Diarrhea'}</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'constipation'}</t>
+          <t>constipation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Constipation'}</t>
+          <t>Constipation</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'blood_in_stool'}</t>
+          <t>blood_in_stool</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Blood in stool'}</t>
+          <t>Blood in stool</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'mucous'}</t>
+          <t>mucous</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Mucous'}</t>
+          <t>Mucous</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_10'}</t>
+          <t>less_than_10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 10'}</t>
+          <t>Less than 10</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'10-20'}</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '10-20'}</t>
+          <t>10-20</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'21-30'}</t>
+          <t>21-30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '21-30'}</t>
+          <t>21-30</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'more_than_30'}</t>
+          <t>more_than_30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'More than 30'}</t>
+          <t>More than 30</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_2_times'}</t>
+          <t>less_than_2_times</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 2 times'}</t>
+          <t>Less than 2 times</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'2-3_times'}</t>
+          <t>2-3_times</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '2-3 times'}</t>
+          <t>2-3 times</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'4-6_times'}</t>
+          <t>4-6_times</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '4-6 times'}</t>
+          <t>4-6 times</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'more_than_6_times'}</t>
+          <t>more_than_6_times</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'More than 6 times'}</t>
+          <t>More than 6 times</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
